--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04 18:51</t>
+          <t>2026-05-05 20:19</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hints_DoubleOrigin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hints_DoubleOrigin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hints_DoubleOrigin'!$A$4:$F$5</definedName>
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 20:19</t>
+          <t>2026-05-08 15:11</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:11</t>
+          <t>2026-05-08 15:54</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54</t>
+          <t>2026-05-08 15:56</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:56</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hints_DoubleOrigin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hints_DoubleOrigin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hints_DoubleOrigin'!$A$4:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hints_DoubleOrigin'!$A$4:$F$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,9 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -88,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -97,12 +95,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -469,13 +461,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -495,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09 00:22</t>
+          <t>2026-06-04 19:42</t>
         </is>
       </c>
     </row>
@@ -531,28 +523,8 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>71-9629</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>46132</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2+ unmatched Origin rows same calendar day — review</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F5"/>
+  <autoFilter ref="A4:F4"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04 19:42</t>
+          <t>2026-06-05 14:46</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:46</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:06</t>
+          <t>2026-06-05 21:22</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:37</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:37</t>
+          <t>2026-06-08 18:47</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:47</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/14_Hints_DoubleOrigin.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>
